--- a/assets/2026臺北數位藝術節_藝術入店.xlsx
+++ b/assets/2026臺北數位藝術節_藝術入店.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\DAF2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A67C7270-455D-4340-ADDD-8531DEA74746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{819D2732-9853-428C-AF94-F9A37A36506E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-16320" yWindow="-120" windowWidth="16440" windowHeight="28320" xr2:uid="{6CF2F47F-369B-4526-8963-C11C1554301C}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="90">
   <si>
     <t>id</t>
   </si>
@@ -475,6 +475,10 @@
   </si>
   <si>
     <t>官網：https://meworldhotel.com/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Miss Coffee Bar</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1020,6 +1024,9 @@
       <c r="B4" s="8" t="s">
         <v>26</v>
       </c>
+      <c r="C4" s="2" t="s">
+        <v>89</v>
+      </c>
       <c r="D4" t="s">
         <v>45</v>
       </c>
